--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Nutri_Hospital\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A701B980-2D47-48DC-882E-2CFEFBEFD7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="38490" yWindow="60" windowWidth="19020" windowHeight="15600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODIET" sheetId="1" r:id="rId1"/>
@@ -13,8 +19,8 @@
     <sheet name="FRESENIUS" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -22,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="181">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -445,13 +451,133 @@
   </si>
   <si>
     <t>Produto</t>
+  </si>
+  <si>
+    <t>DIBEN 1.5</t>
+  </si>
+  <si>
+    <t>1000ML/500ML</t>
+  </si>
+  <si>
+    <t>DIBEN</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY DRINK</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD DRINK</t>
+  </si>
+  <si>
+    <t>FEBRINI ENERGY DRINK</t>
+  </si>
+  <si>
+    <t>FEBRINI ENERGY FIBRE</t>
+  </si>
+  <si>
+    <t>FEBRINI ORIGINAL</t>
+  </si>
+  <si>
+    <t>FEBRINI ORIGINAL FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN 1.2 HP FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2 KCAL CREME</t>
+  </si>
+  <si>
+    <t>125G</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2KCAL DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2KCAL DRINK FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2KCAL HP FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN 2KCAL HP</t>
+  </si>
+  <si>
+    <t>FRESUBIN 3.2 KCAL DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN 5KCAL SHOT</t>
+  </si>
+  <si>
+    <t>120ML</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY FIBRE</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY</t>
+  </si>
+  <si>
+    <t>FRESUBIN HEPA</t>
+  </si>
+  <si>
+    <t>FRESUBIN HP ENERGY FB</t>
+  </si>
+  <si>
+    <t>FRESUBIN HP ENERGY</t>
+  </si>
+  <si>
+    <t>FRESUBIN JUCY DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN LP</t>
+  </si>
+  <si>
+    <t>FRESUBIN PROTEIN ENERGY DRINK</t>
+  </si>
+  <si>
+    <t>FRESUBIN PROTEIN POWDER</t>
+  </si>
+  <si>
+    <t>300g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPPORTAN </t>
+  </si>
+  <si>
+    <t>SUPPORTAN DRINK</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD</t>
+  </si>
+  <si>
+    <t>1000ml</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD HN</t>
+  </si>
+  <si>
+    <t>500ml</t>
+  </si>
+  <si>
+    <t>THICK &amp; EASY</t>
+  </si>
+  <si>
+    <t>225G</t>
+  </si>
+  <si>
+    <t>THICK &amp; EASY CLEAR</t>
+  </si>
+  <si>
+    <t>126G</t>
+  </si>
+  <si>
+    <t>FRESUBIN PRO DRINK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -517,11 +643,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -828,16 +955,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -850,7 +977,7 @@
     <col min="12" max="12" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -888,7 +1015,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -926,7 +1053,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -964,7 +1091,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -1002,7 +1129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>101</v>
       </c>
@@ -1040,7 +1167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -1078,7 +1205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -1116,7 +1243,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1154,7 +1281,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -1192,7 +1319,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -1230,7 +1357,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -1268,7 +1395,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -1306,7 +1433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1471,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -1382,7 +1509,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -1420,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -1458,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -1496,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -1534,7 +1661,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>82</v>
       </c>
@@ -1572,7 +1699,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -1610,7 +1737,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>85</v>
       </c>
@@ -1648,7 +1775,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1686,7 +1813,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -1724,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -1762,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -1800,115 +1927,115 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>92</v>
       </c>
       <c r="B26">
         <v>125</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="7">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7">
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
         <v>0.2</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>2.9</v>
       </c>
-      <c r="I26" s="7">
-        <v>0</v>
-      </c>
-      <c r="J26" s="7">
-        <v>0</v>
-      </c>
-      <c r="K26" s="7">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="I26" s="6">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>7</v>
       </c>
-      <c r="E27" s="7">
-        <v>0</v>
-      </c>
-      <c r="F27" s="7">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7">
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
         <v>0.4</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>5.7</v>
       </c>
-      <c r="I27" s="7">
-        <v>0</v>
-      </c>
-      <c r="J27" s="7">
-        <v>0</v>
-      </c>
-      <c r="K27" s="7">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="I27" s="6">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="7">
-        <v>15</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="D28" s="6">
+        <v>15</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
         <v>0.9</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>11</v>
       </c>
-      <c r="I28" s="7">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7">
-        <v>0</v>
-      </c>
-      <c r="K28" s="7">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="I28" s="6">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -1942,11 +2069,11 @@
       <c r="K29">
         <v>4</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="6">
         <v>0.48</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -1980,7 +2107,7 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1990,9 +2117,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -2004,7 +2131,7 @@
     <col min="12" max="12" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2042,7 +2169,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2080,7 +2207,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2118,7 +2245,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2156,7 +2283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2194,7 +2321,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2232,7 +2359,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2270,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2308,7 +2435,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2346,7 +2473,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>132</v>
       </c>
@@ -2384,7 +2511,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2422,7 +2549,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2460,7 +2587,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>133</v>
       </c>
@@ -2498,7 +2625,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>134</v>
       </c>
@@ -2536,7 +2663,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2574,7 +2701,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2612,7 +2739,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2650,7 +2777,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2688,7 +2815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2726,7 +2853,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -2764,7 +2891,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2802,7 +2929,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -2837,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2875,7 +3002,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -2913,7 +3040,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -2951,7 +3078,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -2989,7 +3116,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -3027,7 +3154,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -3065,7 +3192,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -3103,7 +3230,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -3141,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -3179,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3223,9 +3350,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -3238,7 +3365,7 @@
     <col min="12" max="12" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>140</v>
       </c>
@@ -3276,7 +3403,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75">
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>122</v>
       </c>
@@ -3314,7 +3441,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>123</v>
       </c>
@@ -3352,7 +3479,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>124</v>
       </c>
@@ -3390,11 +3517,11 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -3428,7 +3555,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>121</v>
       </c>
@@ -3466,7 +3593,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -3504,7 +3631,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>139</v>
       </c>
@@ -3542,7 +3669,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -3580,7 +3707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -3618,7 +3745,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -3653,7 +3780,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -3691,7 +3818,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -3729,7 +3856,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -3767,7 +3894,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -3805,7 +3932,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -3843,7 +3970,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.75">
+    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -3881,7 +4008,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75">
+    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>120</v>
       </c>
@@ -3919,7 +4046,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75">
+    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>105</v>
       </c>
@@ -3957,7 +4084,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75">
+    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -3995,7 +4122,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75">
+    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -4033,7 +4160,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75">
+    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -4071,8 +4198,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C23" t="s">
@@ -4106,8 +4233,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C24" t="s">
@@ -4147,10 +4274,1314 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8">
+        <v>150</v>
+      </c>
+      <c r="E2" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="F2" s="8">
+        <v>7</v>
+      </c>
+      <c r="G2" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H2" s="8">
+        <v>55</v>
+      </c>
+      <c r="I2" s="8">
+        <v>2</v>
+      </c>
+      <c r="J2" s="8">
+        <v>180</v>
+      </c>
+      <c r="K2" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="L2" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F3" s="7">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="H3" s="7">
+        <v>85</v>
+      </c>
+      <c r="I3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="J3" s="7">
+        <v>143</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="L3" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7">
+        <v>150</v>
+      </c>
+      <c r="E4" s="7">
+        <v>56</v>
+      </c>
+      <c r="F4" s="7">
+        <v>58</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>80</v>
+      </c>
+      <c r="I4" s="7">
+        <v>2</v>
+      </c>
+      <c r="J4" s="7">
+        <v>135</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7">
+        <v>100</v>
+      </c>
+      <c r="E5" s="7">
+        <v>47</v>
+      </c>
+      <c r="F5" s="7">
+        <v>28</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>80</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
+        <v>200</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7">
+        <v>150</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="F6" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>81</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="J6" s="7">
+        <v>150</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7">
+        <v>150</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="F7" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H7" s="7">
+        <v>81</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="J7" s="7">
+        <v>150</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7">
+        <v>100</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>54</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J8" s="7">
+        <v>100</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7">
+        <v>100</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>4.45</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="7">
+        <v>54</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <v>100</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7">
+        <v>120</v>
+      </c>
+      <c r="E10" s="7">
+        <v>6</v>
+      </c>
+      <c r="F10" s="7">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="H10" s="7">
+        <v>115</v>
+      </c>
+      <c r="I10" s="7">
+        <v>2</v>
+      </c>
+      <c r="J10" s="7">
+        <v>223</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="7">
+        <v>200</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>65</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="J11" s="7">
+        <v>167</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7">
+        <v>200</v>
+      </c>
+      <c r="E12" s="7">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>60</v>
+      </c>
+      <c r="I12" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="J12" s="7">
+        <v>160</v>
+      </c>
+      <c r="K12" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7">
+        <v>200</v>
+      </c>
+      <c r="E13" s="7">
+        <v>10</v>
+      </c>
+      <c r="F13" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="G13" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="H13" s="7">
+        <v>60</v>
+      </c>
+      <c r="I13" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="7">
+        <v>160</v>
+      </c>
+      <c r="K13" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="L13" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7">
+        <v>200</v>
+      </c>
+      <c r="E14" s="7">
+        <v>10</v>
+      </c>
+      <c r="F14" s="7">
+        <v>10</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="7">
+        <v>60</v>
+      </c>
+      <c r="I14" s="7">
+        <v>3</v>
+      </c>
+      <c r="J14" s="7">
+        <v>170</v>
+      </c>
+      <c r="K14" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="L14" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7">
+        <v>200</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15" s="7">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>60</v>
+      </c>
+      <c r="I15" s="7">
+        <v>3</v>
+      </c>
+      <c r="J15" s="7">
+        <v>170</v>
+      </c>
+      <c r="K15" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7">
+        <v>320</v>
+      </c>
+      <c r="E16" s="7">
+        <v>16</v>
+      </c>
+      <c r="F16" s="7">
+        <v>16</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="7">
+        <v>112</v>
+      </c>
+      <c r="I16" s="7">
+        <v>4.8</v>
+      </c>
+      <c r="J16" s="7">
+        <v>312</v>
+      </c>
+      <c r="K16" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L16" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7">
+        <v>500</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>53.8</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7">
+        <v>150</v>
+      </c>
+      <c r="E18" s="7">
+        <v>5.6</v>
+      </c>
+      <c r="F18" s="7">
+        <v>5.8</v>
+      </c>
+      <c r="G18" s="7">
+        <v>150</v>
+      </c>
+      <c r="H18" s="7">
+        <v>100</v>
+      </c>
+      <c r="I18" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="J18" s="7">
+        <v>200</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="L18" s="7">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7">
+        <v>150</v>
+      </c>
+      <c r="E19" s="7">
+        <v>5.6</v>
+      </c>
+      <c r="F19" s="7">
+        <v>5.8</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>100</v>
+      </c>
+      <c r="I19" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="J19" s="7">
+        <v>200</v>
+      </c>
+      <c r="K19" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="L19" s="7">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7">
+        <v>130</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4</v>
+      </c>
+      <c r="F20" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7">
+        <v>75</v>
+      </c>
+      <c r="I20" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="J20" s="7">
+        <v>120</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="L20" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7">
+        <v>150</v>
+      </c>
+      <c r="E21" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="F21" s="7">
+        <v>5.8</v>
+      </c>
+      <c r="G21" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="7">
+        <v>95</v>
+      </c>
+      <c r="I21" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="J21" s="7">
+        <v>234</v>
+      </c>
+      <c r="K21" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="L21" s="7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7">
+        <v>150</v>
+      </c>
+      <c r="E22" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="F22" s="7">
+        <v>5.8</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>120</v>
+      </c>
+      <c r="I22" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="J22" s="7">
+        <v>234</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="L22" s="7">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7">
+        <v>150</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>6</v>
+      </c>
+      <c r="I23" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="J23" s="7">
+        <v>7</v>
+      </c>
+      <c r="K23" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="L23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7">
+        <v>200</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3</v>
+      </c>
+      <c r="F24" s="7">
+        <v>8.9</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="H24" s="7">
+        <v>68</v>
+      </c>
+      <c r="I24" s="7">
+        <v>2</v>
+      </c>
+      <c r="J24" s="7">
+        <v>100</v>
+      </c>
+      <c r="K24" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="L24" s="7">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7">
+        <v>150</v>
+      </c>
+      <c r="E25" s="7">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="7">
+        <v>58</v>
+      </c>
+      <c r="I25" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="J25" s="7">
+        <v>146</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1</v>
+      </c>
+      <c r="L25" s="7">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="7">
+        <v>360</v>
+      </c>
+      <c r="E26" s="7">
+        <v>87</v>
+      </c>
+      <c r="F26" s="7">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>550</v>
+      </c>
+      <c r="I26" s="7">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7">
+        <v>1200</v>
+      </c>
+      <c r="K26" s="7">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7">
+        <v>150</v>
+      </c>
+      <c r="E27" s="7">
+        <v>10</v>
+      </c>
+      <c r="F27" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="G27" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="H27" s="7">
+        <v>47.5</v>
+      </c>
+      <c r="I27" s="7">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7">
+        <v>128</v>
+      </c>
+      <c r="K27" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="L27" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7">
+        <v>150</v>
+      </c>
+      <c r="E28" s="7">
+        <v>10</v>
+      </c>
+      <c r="F28" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="7">
+        <v>50</v>
+      </c>
+      <c r="I28" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="J28" s="7">
+        <v>146</v>
+      </c>
+      <c r="K28" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L28" s="7">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7">
+        <v>100</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="F29" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="G29" s="7">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>80</v>
+      </c>
+      <c r="I29" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="J29" s="7">
+        <v>200</v>
+      </c>
+      <c r="K29" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="L29" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="7">
+        <v>100</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="F30" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="G30" s="7">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>80</v>
+      </c>
+      <c r="I30" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="J30" s="7">
+        <v>200</v>
+      </c>
+      <c r="K30" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="L30" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="7">
+        <v>133</v>
+      </c>
+      <c r="E31" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="F31" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="G31" s="7">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>135</v>
+      </c>
+      <c r="I31" s="7">
+        <v>2</v>
+      </c>
+      <c r="J31" s="7">
+        <v>260</v>
+      </c>
+      <c r="K31" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="L31" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="7">
+        <v>373</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>174</v>
+      </c>
+      <c r="I32" s="7">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="7">
+        <v>291.10000000000002</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>31.2</v>
+      </c>
+      <c r="H33" s="7">
+        <v>1344</v>
+      </c>
+      <c r="I33" s="7">
+        <v>0</v>
+      </c>
+      <c r="J33" s="7">
+        <v>449</v>
+      </c>
+      <c r="K33" s="7">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="7">
+        <v>240</v>
+      </c>
+      <c r="E34" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="F34" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>30</v>
+      </c>
+      <c r="I34" s="7">
+        <v>2</v>
+      </c>
+      <c r="J34" s="7">
+        <v>87</v>
+      </c>
+      <c r="K34" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L34" s="7">
+        <v>0.72</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>